--- a/data/processed/harmonization/Acidity__Soil_pH/10.5440_1618325/10.5440_1618325_soil_Acidity__Soil_pH.xlsx
+++ b/data/processed/harmonization/Acidity__Soil_pH/10.5440_1618325/10.5440_1618325_soil_Acidity__Soil_pH.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -557,7 +557,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -669,7 +669,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pH_KCl</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage</t>
+          <t>lat/long source: doi:10.5440/1618325 metadata bounding box centre (±9.9 km); source column Soil_pH; depth from Upper_depth_cm, Lower_depth_cm; date 2015-10-15 from package temporal coverage; method from NGEE_User_Guidance_Document_template_BEO_SoilFe_20200515.pdf</t>
         </is>
       </c>
     </row>
